--- a/data/trans_orig/DCD-Edad-trans_orig.xlsx
+++ b/data/trans_orig/DCD-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2012</t>
+          <t>Población con dolor crónico discapacitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31550</t>
+          <t>30740</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +782,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>26225</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>17264</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>37785</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>26225</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>17192</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>38990</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442095</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452191</t>
+          <t>452132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>398680</t>
+          <t>399490</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>417449</t>
+          <t>417382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +895,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>858151</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>846591</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>867112</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>97,03%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>858151</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>845386</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>867184</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28911</t>
+          <t>28990</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30337</t>
+          <t>29981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54533</t>
+          <t>56438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45749</t>
+          <t>44311</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77661</t>
+          <t>76925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>658176</t>
+          <t>658097</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>676131</t>
+          <t>675223</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555722</t>
+          <t>553817</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>579918</t>
+          <t>580274</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1219681</t>
+          <t>1220417</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1251593</t>
+          <t>1253031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41413</t>
+          <t>41285</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67701</t>
+          <t>67988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103828</t>
+          <t>103761</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92680</t>
+          <t>90637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134375</t>
+          <t>135753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640450</t>
+          <t>640578</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662363</t>
+          <t>661911</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>607022</t>
+          <t>607089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>643149</t>
+          <t>642862</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1258337</t>
+          <t>1256959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1300032</t>
+          <t>1302075</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28344</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>56607</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72193</t>
+          <t>71409</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108720</t>
+          <t>108648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110256</t>
+          <t>108656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152943</t>
+          <t>154445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>560901</t>
+          <t>558010</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>586273</t>
+          <t>585697</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>507479</t>
+          <t>507551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>544006</t>
+          <t>544790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1077873</t>
+          <t>1076371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1120560</t>
+          <t>1122160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26690</t>
+          <t>26707</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50266</t>
+          <t>50722</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79314</t>
+          <t>77456</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115430</t>
+          <t>115464</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113460</t>
+          <t>112064</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156457</t>
+          <t>155261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>379163</t>
+          <t>378707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>402739</t>
+          <t>402722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>332370</t>
+          <t>332336</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>368486</t>
+          <t>370344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>720772</t>
+          <t>721968</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>763769</t>
+          <t>765165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33983</t>
+          <t>34157</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60168</t>
+          <t>61184</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83271</t>
+          <t>84849</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116648</t>
+          <t>117876</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126473</t>
+          <t>125601</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>168729</t>
+          <t>168458</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249618</t>
+          <t>248602</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>275803</t>
+          <t>275629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237348</t>
+          <t>236120</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270725</t>
+          <t>269147</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>495053</t>
+          <t>495324</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>537309</t>
+          <t>538181</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38533</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64444</t>
+          <t>65709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129461</t>
+          <t>130083</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169192</t>
+          <t>169948</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>176448</t>
+          <t>177260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>224476</t>
+          <t>227037</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185407</t>
+          <t>184142</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>211318</t>
+          <t>211446</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>219787</t>
+          <t>219031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>259518</t>
+          <t>258896</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>414354</t>
+          <t>411793</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>462382</t>
+          <t>461570</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>199449</t>
+          <t>198343</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>260328</t>
+          <t>256990</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>537033</t>
+          <t>537418</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>626371</t>
+          <t>624984</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>757863</t>
+          <t>753113</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>861259</t>
+          <t>862980</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3166451</t>
+          <t>3169789</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3227330</t>
+          <t>3228436</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2931938</t>
+          <t>2933325</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3021276</t>
+          <t>3020891</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6123829</t>
+          <t>6122108</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6227225</t>
+          <t>6231975</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2016</t>
+          <t>Población con dolor crónico discapacitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21884</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412483</t>
+          <t>413322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>373871</t>
+          <t>374384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>387873</t>
+          <t>387966</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>790692</t>
+          <t>791322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>805697</t>
+          <t>806286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>29046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>26311</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50696</t>
+          <t>49671</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40487</t>
+          <t>41548</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70285</t>
+          <t>70153</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>561390</t>
+          <t>561450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>580310</t>
+          <t>580509</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512848</t>
+          <t>513873</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>536926</t>
+          <t>537233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1083755</t>
+          <t>1083887</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1113553</t>
+          <t>1112492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38671</t>
+          <t>38316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45278</t>
+          <t>44158</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75036</t>
+          <t>74563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67589</t>
+          <t>66875</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104020</t>
+          <t>103731</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>630426</t>
+          <t>630781</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652044</t>
+          <t>651907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>586350</t>
+          <t>586823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>616108</t>
+          <t>617228</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1226463</t>
+          <t>1226752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1262894</t>
+          <t>1263608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30116</t>
+          <t>30205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56605</t>
+          <t>56508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>68342</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103606</t>
+          <t>103393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104427</t>
+          <t>104433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149573</t>
+          <t>148581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>589443</t>
+          <t>589540</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>615932</t>
+          <t>615843</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>545471</t>
+          <t>545684</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>582006</t>
+          <t>580735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1145552</t>
+          <t>1146544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1190698</t>
+          <t>1190692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45178</t>
+          <t>44918</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75182</t>
+          <t>73917</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72166</t>
+          <t>72197</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106535</t>
+          <t>107769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124854</t>
+          <t>123858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172342</t>
+          <t>173958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>402736</t>
+          <t>404001</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>432740</t>
+          <t>433000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>390314</t>
+          <t>389080</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424683</t>
+          <t>424652</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>802425</t>
+          <t>800809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>849913</t>
+          <t>850909</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,29%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22255</t>
+          <t>22452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45449</t>
+          <t>44701</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51157</t>
+          <t>52399</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80940</t>
+          <t>82209</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79566</t>
+          <t>81297</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116300</t>
+          <t>118713</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288881</t>
+          <t>289629</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>312075</t>
+          <t>311878</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>296822</t>
+          <t>295553</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>326605</t>
+          <t>325363</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>595792</t>
+          <t>593379</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>632526</t>
+          <t>630795</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,58%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39808</t>
+          <t>39108</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63738</t>
+          <t>63219</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>96999</t>
+          <t>96252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136531</t>
+          <t>135226</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>143215</t>
+          <t>141507</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>192496</t>
+          <t>190005</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193260</t>
+          <t>193779</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>217190</t>
+          <t>217890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>263638</t>
+          <t>264943</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>303170</t>
+          <t>303917</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>464671</t>
+          <t>467162</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>513952</t>
+          <t>515660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,47%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>199191</t>
+          <t>199386</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>260919</t>
+          <t>259359</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>422039</t>
+          <t>425440</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>505227</t>
+          <t>510224</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>639330</t>
+          <t>638683</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>743382</t>
+          <t>741169</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3133431</t>
+          <t>3134991</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3195159</t>
+          <t>3194964</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3039315</t>
+          <t>3034318</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3122503</t>
+          <t>3119102</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6195510</t>
+          <t>6197723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6299562</t>
+          <t>6300209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2023</t>
+          <t>Población con dolor crónico discapacitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35761</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72660</t>
+          <t>72502</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38377</t>
+          <t>41304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79656</t>
+          <t>82452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>379724</t>
+          <t>380487</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398008</t>
+          <t>397995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240540</t>
+          <t>240698</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277439</t>
+          <t>278048</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>633531</t>
+          <t>630735</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>674810</t>
+          <t>671883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11982</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33571</t>
+          <t>34005</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>38721</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84558</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59285</t>
+          <t>62676</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106588</t>
+          <t>107221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389976</t>
+          <t>389542</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411565</t>
+          <t>411229</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427535</t>
+          <t>427646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>473916</t>
+          <t>473372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>829052</t>
+          <t>828419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>876355</t>
+          <t>872964</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>29546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56384</t>
+          <t>55897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71923</t>
+          <t>70956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112253</t>
+          <t>112457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111341</t>
+          <t>112821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156669</t>
+          <t>159019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479954</t>
+          <t>480441</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>506853</t>
+          <t>506792</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>479749</t>
+          <t>479545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>520079</t>
+          <t>521046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>971671</t>
+          <t>969321</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1016999</t>
+          <t>1015519</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38280</t>
+          <t>39716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131716</t>
+          <t>134003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142292</t>
+          <t>143432</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189891</t>
+          <t>190872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149432</t>
+          <t>164923</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315420</t>
+          <t>320612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>756070</t>
+          <t>753783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>849506</t>
+          <t>848070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522990</t>
+          <t>522009</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>570589</t>
+          <t>569449</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1285247</t>
+          <t>1280055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1451235</t>
+          <t>1435744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>89,7%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95276</t>
+          <t>96738</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131000</t>
+          <t>132931</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>157359</t>
+          <t>156958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189460</t>
+          <t>188757</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>262789</t>
+          <t>263175</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>311526</t>
+          <t>312063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430234</t>
+          <t>428303</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465958</t>
+          <t>464496</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>358445</t>
+          <t>359148</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>390546</t>
+          <t>390947</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>797613</t>
+          <t>797076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>846350</t>
+          <t>845964</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,27%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55760</t>
+          <t>56484</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78539</t>
+          <t>80576</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54699</t>
+          <t>59646</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>205753</t>
+          <t>208779</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111828</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>263128</t>
+          <t>261653</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289626</t>
+          <t>287589</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>312405</t>
+          <t>311681</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>402615</t>
+          <t>399589</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>553669</t>
+          <t>548722</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>713405</t>
+          <t>714880</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>864705</t>
+          <t>867973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,88%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73877</t>
+          <t>72900</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97054</t>
+          <t>96556</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>200327</t>
+          <t>199127</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>229710</t>
+          <t>231801</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>280262</t>
+          <t>279868</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>319947</t>
+          <t>318129</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185705</t>
+          <t>186203</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208882</t>
+          <t>209859</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>196121</t>
+          <t>194030</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>225504</t>
+          <t>226704</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>388643</t>
+          <t>390461</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>428328</t>
+          <t>428722</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,5%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>337616</t>
+          <t>336018</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>477084</t>
+          <t>476740</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>736624</t>
+          <t>722617</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>976182</t>
+          <t>975036</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1154101</t>
+          <t>1138230</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1428993</t>
+          <t>1424504</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2982733</t>
+          <t>2983077</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3122201</t>
+          <t>3123799</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2736098</t>
+          <t>2737244</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2975656</t>
+          <t>2989663</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5743104</t>
+          <t>5747593</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6017996</t>
+          <t>6033867</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DCD-Edad-trans_orig.xlsx
+++ b/data/trans_orig/DCD-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30740</t>
+          <t>31144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>17950</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37785</t>
+          <t>37812</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441942</t>
+          <t>441566</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452132</t>
+          <t>452195</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399490</t>
+          <t>399086</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>417382</t>
+          <t>417321</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>846591</t>
+          <t>846564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>867112</t>
+          <t>866426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28990</t>
+          <t>30166</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56438</t>
+          <t>56042</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44311</t>
+          <t>45327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76925</t>
+          <t>76137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>658097</t>
+          <t>656921</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>675223</t>
+          <t>675205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>553817</t>
+          <t>554213</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>580274</t>
+          <t>580277</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1220417</t>
+          <t>1221205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1253031</t>
+          <t>1252015</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41285</t>
+          <t>43022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67988</t>
+          <t>65888</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103761</t>
+          <t>102992</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90637</t>
+          <t>93288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135753</t>
+          <t>134393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640578</t>
+          <t>638841</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661911</t>
+          <t>662485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>607089</t>
+          <t>607858</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>642862</t>
+          <t>644962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1256959</t>
+          <t>1258319</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1302075</t>
+          <t>1299424</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28920</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56607</t>
+          <t>54332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71409</t>
+          <t>72443</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108648</t>
+          <t>109862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108656</t>
+          <t>109381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154445</t>
+          <t>152594</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>558010</t>
+          <t>560285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>585697</t>
+          <t>585730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>507551</t>
+          <t>506337</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>544790</t>
+          <t>543756</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1076371</t>
+          <t>1078222</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1122160</t>
+          <t>1121435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26707</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50722</t>
+          <t>48971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77456</t>
+          <t>78833</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115464</t>
+          <t>113587</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112064</t>
+          <t>113707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155261</t>
+          <t>156655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>378707</t>
+          <t>380458</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>402722</t>
+          <t>402659</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>332336</t>
+          <t>334213</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>370344</t>
+          <t>368967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>721968</t>
+          <t>720574</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>765165</t>
+          <t>763522</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34157</t>
+          <t>34615</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61184</t>
+          <t>60540</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84849</t>
+          <t>82926</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117876</t>
+          <t>116857</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>125601</t>
+          <t>125312</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>168458</t>
+          <t>169414</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248602</t>
+          <t>249246</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>275629</t>
+          <t>275171</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236120</t>
+          <t>237139</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269147</t>
+          <t>271070</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>495324</t>
+          <t>494368</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>538181</t>
+          <t>538470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,12%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>37689</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65709</t>
+          <t>63634</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130083</t>
+          <t>129271</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169948</t>
+          <t>170184</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>177260</t>
+          <t>176456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227037</t>
+          <t>224986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>184142</t>
+          <t>186217</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>211446</t>
+          <t>212162</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>219031</t>
+          <t>218795</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258896</t>
+          <t>259708</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>411793</t>
+          <t>413844</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>461570</t>
+          <t>462374</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,38%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>198343</t>
+          <t>198146</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>256990</t>
+          <t>256925</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>537418</t>
+          <t>536814</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>624984</t>
+          <t>626754</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>753113</t>
+          <t>757979</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>862980</t>
+          <t>871047</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3169789</t>
+          <t>3169854</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3228436</t>
+          <t>3228633</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2933325</t>
+          <t>2931555</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3020891</t>
+          <t>3021495</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6122108</t>
+          <t>6114041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6231975</t>
+          <t>6227109</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23896</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413322</t>
+          <t>412544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>374384</t>
+          <t>374431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>387966</t>
+          <t>387265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>791322</t>
+          <t>790456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>806286</t>
+          <t>806242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29046</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>27059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49671</t>
+          <t>51759</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41548</t>
+          <t>41326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70153</t>
+          <t>70178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>561450</t>
+          <t>561557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>580509</t>
+          <t>580275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513873</t>
+          <t>511785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>537233</t>
+          <t>536485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1083887</t>
+          <t>1083862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1112492</t>
+          <t>1112714</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17190</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38316</t>
+          <t>37951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44158</t>
+          <t>45631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74563</t>
+          <t>75786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66875</t>
+          <t>69025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103731</t>
+          <t>102976</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>630781</t>
+          <t>631146</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651907</t>
+          <t>652530</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>586823</t>
+          <t>585600</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>617228</t>
+          <t>615755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1226752</t>
+          <t>1227507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1263608</t>
+          <t>1261458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30205</t>
+          <t>30433</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56508</t>
+          <t>55087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68342</t>
+          <t>68256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103393</t>
+          <t>102364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104433</t>
+          <t>105027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148581</t>
+          <t>148496</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>589540</t>
+          <t>590961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>615843</t>
+          <t>615615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>545684</t>
+          <t>546713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>580735</t>
+          <t>580821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1146544</t>
+          <t>1146629</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1190692</t>
+          <t>1190098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44918</t>
+          <t>43739</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73917</t>
+          <t>75581</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72197</t>
+          <t>73073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107769</t>
+          <t>108997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123858</t>
+          <t>125416</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>173958</t>
+          <t>172490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>404001</t>
+          <t>402337</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>433000</t>
+          <t>434179</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>389080</t>
+          <t>387852</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424652</t>
+          <t>423776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>800809</t>
+          <t>802277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>850909</t>
+          <t>849351</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22452</t>
+          <t>22085</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44701</t>
+          <t>44831</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52399</t>
+          <t>52404</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82209</t>
+          <t>81589</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81297</t>
+          <t>80889</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118713</t>
+          <t>116850</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289629</t>
+          <t>289499</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>311878</t>
+          <t>312245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>295553</t>
+          <t>296173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325363</t>
+          <t>325358</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>593379</t>
+          <t>595242</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>630795</t>
+          <t>631203</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,64%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39108</t>
+          <t>38892</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63219</t>
+          <t>62999</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>96252</t>
+          <t>94789</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>135226</t>
+          <t>134548</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>141507</t>
+          <t>143171</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>190005</t>
+          <t>190659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193779</t>
+          <t>193999</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>217890</t>
+          <t>218106</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>264943</t>
+          <t>265621</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>303917</t>
+          <t>305380</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>467162</t>
+          <t>466508</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>515660</t>
+          <t>513996</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,21%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>199386</t>
+          <t>201723</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>259359</t>
+          <t>258952</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>425440</t>
+          <t>422673</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>510224</t>
+          <t>503963</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>638683</t>
+          <t>642058</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>741169</t>
+          <t>743100</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3134991</t>
+          <t>3135398</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3194964</t>
+          <t>3192627</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3034318</t>
+          <t>3040579</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3119102</t>
+          <t>3121869</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6197723</t>
+          <t>6195792</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6300209</t>
+          <t>6296834</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,75%</t>
         </is>
       </c>
     </row>
@@ -6685,32 +6685,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6720,32 +6720,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50324</t>
+          <t>60871</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35152</t>
+          <t>42431</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72502</t>
+          <t>82765</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6755,32 +6755,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>67799</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41304</t>
+          <t>47688</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82452</t>
+          <t>95229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -6798,32 +6798,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>392781</t>
+          <t>400865</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>380487</t>
+          <t>388680</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397995</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6833,32 +6833,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>262876</t>
+          <t>301641</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240698</t>
+          <t>279747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>278048</t>
+          <t>320081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6868,32 +6868,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>655656</t>
+          <t>702506</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>630735</t>
+          <t>675076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>671883</t>
+          <t>722617</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -6911,17 +6911,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6981,17 +6981,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7028,32 +7028,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34005</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7063,32 +7063,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64231</t>
+          <t>69185</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38721</t>
+          <t>52963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84447</t>
+          <t>86179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7098,32 +7098,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>84468</t>
+          <t>92866</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62676</t>
+          <t>73080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107221</t>
+          <t>114214</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -7141,32 +7141,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>403310</t>
+          <t>453209</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389542</t>
+          <t>438620</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411229</t>
+          <t>463521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7176,32 +7176,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447862</t>
+          <t>432548</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427646</t>
+          <t>415554</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>473372</t>
+          <t>448770</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7211,32 +7211,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>851172</t>
+          <t>885757</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>828419</t>
+          <t>864409</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>872964</t>
+          <t>905543</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -7254,17 +7254,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7371,32 +7371,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>41234</t>
+          <t>43275</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>30722</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55897</t>
+          <t>57588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7406,32 +7406,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>94645</t>
+          <t>110551</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70956</t>
+          <t>95867</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112457</t>
+          <t>130039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7441,32 +7441,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>135879</t>
+          <t>153827</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112821</t>
+          <t>133736</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159019</t>
+          <t>177369</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -7484,32 +7484,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>495104</t>
+          <t>577562</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>480441</t>
+          <t>563249</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>506792</t>
+          <t>590115</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7519,32 +7519,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>497357</t>
+          <t>512642</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>479545</t>
+          <t>493154</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>521046</t>
+          <t>527326</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7554,32 +7554,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>992461</t>
+          <t>1090202</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>969321</t>
+          <t>1066660</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1015519</t>
+          <t>1110293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -7597,17 +7597,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>89870</t>
+          <t>95227</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39716</t>
+          <t>78092</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134003</t>
+          <t>115100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>168927</t>
+          <t>181708</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143432</t>
+          <t>163807</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>190872</t>
+          <t>201724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>258797</t>
+          <t>276935</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164923</t>
+          <t>251219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>320612</t>
+          <t>304641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7827,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>797916</t>
+          <t>605390</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>753783</t>
+          <t>585517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>848070</t>
+          <t>622525</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7862,32 +7862,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>543954</t>
+          <t>555178</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522009</t>
+          <t>535162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>569449</t>
+          <t>573079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1341870</t>
+          <t>1160569</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1280055</t>
+          <t>1132863</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1435744</t>
+          <t>1186285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>113477</t>
+          <t>118949</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96738</t>
+          <t>101537</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132931</t>
+          <t>138663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>173924</t>
+          <t>191528</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>156958</t>
+          <t>174161</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188757</t>
+          <t>208907</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>287401</t>
+          <t>310477</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>263175</t>
+          <t>283693</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>312063</t>
+          <t>340158</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>447757</t>
+          <t>490397</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>428303</t>
+          <t>470683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>464496</t>
+          <t>507809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>373981</t>
+          <t>417327</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>359148</t>
+          <t>399948</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>390947</t>
+          <t>434694</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8240,32 +8240,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>821738</t>
+          <t>907725</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>797076</t>
+          <t>878044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>845964</t>
+          <t>934509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,71%</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8400,32 +8400,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>67209</t>
+          <t>72921</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56484</t>
+          <t>59586</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80576</t>
+          <t>86532</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>133024</t>
+          <t>147273</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59646</t>
+          <t>133015</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>208779</t>
+          <t>162173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>200234</t>
+          <t>220194</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>108560</t>
+          <t>201515</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>261653</t>
+          <t>242666</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -8513,32 +8513,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>300956</t>
+          <t>334159</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287589</t>
+          <t>320548</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>311681</t>
+          <t>347494</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8548,32 +8548,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>475344</t>
+          <t>291893</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>399589</t>
+          <t>276993</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>548722</t>
+          <t>306151</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8583,32 +8583,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>776299</t>
+          <t>626052</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>714880</t>
+          <t>603580</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>867973</t>
+          <t>644731</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8743,32 +8743,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>84812</t>
+          <t>93930</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72900</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96556</t>
+          <t>108028</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8778,32 +8778,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>214876</t>
+          <t>236792</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>199127</t>
+          <t>219655</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>231801</t>
+          <t>251396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8813,32 +8813,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>299688</t>
+          <t>330722</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>279868</t>
+          <t>308924</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>318129</t>
+          <t>350074</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -8856,32 +8856,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>197947</t>
+          <t>216268</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>186203</t>
+          <t>202170</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>209859</t>
+          <t>230193</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8891,32 +8891,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>210955</t>
+          <t>227817</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>194030</t>
+          <t>213213</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>226704</t>
+          <t>244954</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8926,32 +8926,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>408902</t>
+          <t>444085</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>390461</t>
+          <t>424733</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>428722</t>
+          <t>465883</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,13%</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>424045</t>
+          <t>454911</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>336018</t>
+          <t>418162</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>476740</t>
+          <t>503157</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>899952</t>
+          <t>997910</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>722617</t>
+          <t>952398</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>975036</t>
+          <t>1048222</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1323997</t>
+          <t>1452821</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1138230</t>
+          <t>1385950</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1424504</t>
+          <t>1517258</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3035772</t>
+          <t>3077851</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2983077</t>
+          <t>3029605</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3123799</t>
+          <t>3114600</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9234,32 +9234,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2812328</t>
+          <t>2739044</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2737244</t>
+          <t>2688732</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2989663</t>
+          <t>2784556</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9269,32 +9269,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5848100</t>
+          <t>5816895</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5747593</t>
+          <t>5752458</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6033867</t>
+          <t>5883766</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9312,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
